--- a/reward/task1_bounty.xlsx
+++ b/reward/task1_bounty.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="188">
   <si>
     <t>folder</t>
   </si>
@@ -249,6 +249,12 @@
   </si>
   <si>
     <t>JackCC703</t>
+  </si>
+  <si>
+    <t>aleo142k0nm4uwt2df06krr4fqkslaecgqz58ggjrnslzxt2xu5lexuxszm93cr</t>
+  </si>
+  <si>
+    <t>https://explorer.provable.com/transaction/at128yalhwr35z4eytfatle9dkfw4040ep7hlld8hly3zv7mkvpnczs0arefv?utm_source=shield</t>
   </si>
   <si>
     <t>JasonRUAN</t>
@@ -1752,7 +1758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:I53"/>
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
   <cols>
@@ -1938,7 +1944,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:8">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2022,7 +2028,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:8">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2048,7 +2054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:8">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -2132,7 +2138,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:8">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2303,7 +2309,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:8">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>72</v>
       </c>
@@ -2326,12 +2332,15 @@
         <v>72</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>73</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -2346,21 +2355,21 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -2375,21 +2384,21 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -2404,21 +2413,21 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
@@ -2433,21 +2442,21 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -2462,21 +2471,21 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" hidden="1" spans="1:8">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -2491,10 +2500,10 @@
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
@@ -2502,7 +2511,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -2517,21 +2526,21 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" hidden="1" spans="1:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -2546,10 +2555,10 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
         <v>30</v>
@@ -2557,7 +2566,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -2572,21 +2581,21 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -2601,21 +2610,21 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
@@ -2630,21 +2639,21 @@
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" hidden="1" spans="1:8">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -2659,10 +2668,10 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H32" t="s">
         <v>30</v>
@@ -2670,7 +2679,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -2685,21 +2694,21 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" hidden="1" spans="1:8">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
@@ -2714,10 +2723,10 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H34" t="s">
         <v>30</v>
@@ -2725,7 +2734,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -2740,21 +2749,21 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -2769,21 +2778,21 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G36" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -2798,21 +2807,21 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G37" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
@@ -2827,21 +2836,21 @@
         <v>11</v>
       </c>
       <c r="F38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" hidden="1" spans="1:8">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -2856,10 +2865,10 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H39" t="s">
         <v>30</v>
@@ -2867,7 +2876,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
@@ -2882,21 +2891,21 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" hidden="1" spans="1:8">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -2911,10 +2920,10 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H41" t="s">
         <v>30</v>
@@ -2922,7 +2931,7 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
@@ -2937,21 +2946,21 @@
         <v>11</v>
       </c>
       <c r="F42" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H42" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
@@ -2966,21 +2975,21 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H43" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" hidden="1" spans="1:8">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
@@ -2995,18 +3004,18 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G44" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H44" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:8">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -3021,18 +3030,18 @@
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
@@ -3047,21 +3056,21 @@
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
@@ -3076,21 +3085,21 @@
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H47" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
@@ -3105,21 +3114,21 @@
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G48" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
@@ -3134,21 +3143,21 @@
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
@@ -3163,21 +3172,21 @@
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" hidden="1" spans="1:8">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
@@ -3192,18 +3201,18 @@
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G51" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H51" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:8">
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
@@ -3218,18 +3227,18 @@
         <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H52" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="53" hidden="1" spans="1:8">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
@@ -3244,63 +3253,16 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H53" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H53" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Y"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="aleo1cgmmrhnx050u2yksfp6gs0ztjgp2v3x6zjr2pvn5vdfxh0uguy8sjr668q"/>
-        <filter val="aleo189r8wnj3tc2t9meap272hz72wtq6c2c8jpvhggrxnlzu022fkuqqdv3kla"/>
-        <filter val="aleo18kvx4atvn22j6qrnt8efhzskp5lhk3re0c0ewnp9z3a9tmcreyrsszx2cd"/>
-        <filter val="aleo12edyx9nsxl62g68pdkrpudtruzhykpt87fs89r0an770fvmercyqtv3rs5"/>
-        <filter val="aleo1vutpyav5vwtuge7yg56dswzdchuyupyve4qxs6p3mln2ksw2zuyqza695f"/>
-        <filter val="aleo1lqkc6r53r3dym3cdhvfjhc64f6mvuupamuxq6hfd278qnal5yq9qukw6x7"/>
-        <filter val="aleo18v6cmfrq5dv7sdp24a4aq4jvegf2tp9px33rg7f3f9qply5wavysgp05m8"/>
-        <filter val="aleo169ggxpafd2d8zg36tyytw82qkypmgz3cmswqpf4wkh63ph763szqm02zeh"/>
-        <filter val="aleo1s59tyrcr79jmj9glj289adncasjakzavr6npkcc7jkwqwx0yavzq99rv09"/>
-        <filter val="aleo15wqmf6fjskw6ya6gqv28qkfr4jn8tyjjg53wm5npfz5pm9c4hvqsg5333l"/>
-        <filter val="aleo1ntxq2hsvnh4s5rmh23z2hvdlkd5j97mrxpjutk0ze6nys7ll25zquq3zyr"/>
-        <filter val="aleo1j09wuh7s6jfkgfr6ervkyn7un2u0l0tqsmv82mdq3ycma87up5ysr2w6xs"/>
-        <filter val="aleo1yn9gfx7qy2cz488dktu4w62d9fulvvry6r3pka00983p7hzrlgyq7xltrc"/>
-        <filter val="aleo18tjg2nu8hvvyeuzj0qfx4j2xyfta4q2dnr5wnv8lgv4lq9rrmq8qnxr5h5"/>
-        <filter val="aleo1pxlq66rn0r7du7w346j0c3k62lr8nungvtxw34lt7qkc36tnlu9qdzevmu"/>
-        <filter val="aleo12erak78257x3q2zfy2fdlzd4lw49sr4a5hlm98wsyhp4zyg0zc9s05ual6"/>
-        <filter val="aleo1mvcxge4cawjgenjle7n6w4mycnxq3gzpvy84z2ejhfukzg0pgq9qk9qupv"/>
-        <filter val="aleo1lkp6q3tmpusvxsf37ar8jc9835r07pyrsl9c9qyp4supmmuvavqs2ytf9w"/>
-        <filter val="aleo1n6rppr6n48ms5jp0zahrfdlqmgwzy7pemnayh8mxkhglpkzjgqysgckgd7"/>
-        <filter val="aleo192xccjkqdp5c8lwjdp9ldky5egun3jrg4m2fh05r0tldq8cu9qqqv847yj"/>
-        <filter val="aleo1h5utc52enn9nxn7hknz6xdl9j82ym0vvmh9sdd289u3n7cs96sgq2v9eu2"/>
-        <filter val="aleo1hxrwn37uvt8jm5cks6wvxk44vx6vcgtmvwcsygqamuq6gr4ywuxs000q0w"/>
-        <filter val="aleo1y5x3tjp4zezayr6733edt9c85vv0x8cls2tdy69a0tyksu6vqcyqs3nu8w"/>
-        <filter val="aleo1u69mfdzk2kvrqduwpxwfn2ykk9wa35rw8fxwym3cddkjs2wu8c9s4hegm8"/>
-        <filter val="aleo14sv5c2t9283tfwc2tz89hfhsyrmcqvd0dedft82z69z5sqvtpupqav5548"/>
-        <filter val="aleo1e8ay9hem7c3q4pnmsgdvhqjnn3ks05van6w2f5lvxh29jjav9yzqzlkzaz"/>
-        <filter val="aleo18u0525gjk0j6smncv8u5c55dft4fvkm76700jyd5th7jqkqaqsgs5qupuj"/>
-        <filter val="aleo1jx3ppd0t5st7a6gn6w3gkmdqhwpmwxdf9dq2jz77wz4z0lh29qpsv3ners"/>
-        <filter val="aleo16mkgnu2cmr53nq0l92qylqlczl2gws8elcafdqmurvef5dgrsgrsny85j4"/>
-        <filter val="aleo1uszlvmjmud64ylkzx6zumxznpz6csyutmgv99s9hhafepxpdly8su3xn25"/>
-        <filter val="aleo12scte9sfy3xym23xfhwpgln4tpjqf9t20yn99xsglszjtf4mgggs6z9r46"/>
-        <filter val="aleo1veez9g7f6n2de55cxggtcq475sdfsf0dx2xwcf7rgxm3ze6stuyskl863w"/>
-        <filter val="aleo130pfw9t4g9g0tj68rpg39v8e57jg08wk6dq8wejas9lj0h9egugsst047x"/>
-        <filter val="aleo1vwsyyscy5d8pekfmzc5q9rsyux5erehlrkg86wn45upauk7qfgxse08zwm"/>
-        <filter val="aleo1z3cm5n3rprwmmz9neeavynzprvum2ae5568mdslwl6r6zg4r4gxqdaq8hn"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <conditionalFormatting sqref="G$1:G$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -3341,6 +3303,7 @@
     <hyperlink ref="I48" r:id="rId34" display="https://explorer.provable.com/transaction/at1utq837uqj63mg77lqznxw7yhwpuxeqnwqrpwpcqxpnlp96cpnvpqkt5rre?utm_source=shield"/>
     <hyperlink ref="I49" r:id="rId35" display="https://explorer.provable.com/transaction/at1ks5sqkwv8pcwl38466lu9fdetwnm086uhhurlapcjvlw7ppcxu9sknjytd?utm_source=shield"/>
     <hyperlink ref="I50" r:id="rId36" display="https://explorer.provable.com/transaction/at1jne56rhc5jfl6k8pq0m8n4kf8042n5ydmh25vjw0vv2mxrmtsyrsnwewey?utm_source=shield"/>
+    <hyperlink ref="I20" r:id="rId37" display="https://explorer.provable.com/transaction/at128yalhwr35z4eytfatle9dkfw4040ep7hlld8hly3zv7mkvpnczs0arefv?utm_source=shield" tooltip="https://explorer.provable.com/transaction/at128yalhwr35z4eytfatle9dkfw4040ep7hlld8hly3zv7mkvpnczs0arefv?utm_source=shield"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
